--- a/backtest_runs/20260410_193731/by_symbol/PKGP/PKGP.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/PKGP/PKGP.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -633,7 +633,7 @@
         <v>-936.1000000000017</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" s="3" t="n">
         <v>99063.89999999999</v>
@@ -679,7 +679,7 @@
         <v>-7529.500000000005</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>91534.39999999999</v>
@@ -768,10 +768,10 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>98860.39999999999</v>
@@ -863,7 +863,7 @@
         <v>-1282.049999999991</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K9" s="3" t="n">
         <v>97578.35000000001</v>
@@ -955,7 +955,7 @@
         <v>-1668.700000000001</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K11" s="3" t="n">
         <v>95909.65000000001</v>
@@ -1093,7 +1093,7 @@
         <v>-3093.199999999992</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K14" s="3" t="n">
         <v>110073.25</v>
@@ -1139,7 +1139,7 @@
         <v>-691.9000000000069</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K15" s="3" t="n">
         <v>109381.35</v>
@@ -1185,7 +1185,7 @@
         <v>-2197.799999999997</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>107183.55</v>
@@ -1277,7 +1277,7 @@
         <v>-4090.349999999996</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>106247.45</v>
@@ -1323,7 +1323,7 @@
         <v>-284.9000000000012</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K19" s="3" t="n">
         <v>105962.55</v>
@@ -1369,7 +1369,7 @@
         <v>-1241.349999999999</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K20" s="3" t="n">
         <v>104721.2</v>
@@ -1415,7 +1415,7 @@
         <v>-3113.550000000002</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="3" t="n">
         <v>101607.65</v>
@@ -1458,10 +1458,10 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>101607.65</v>
@@ -1507,7 +1507,7 @@
         <v>-2319.900000000001</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K23" s="3" t="n">
         <v>99287.75</v>
@@ -1642,10 +1642,10 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>104985.75</v>
